--- a/Result/profitability/1264.xlsx
+++ b/Result/profitability/1264.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM55"/>
+  <dimension ref="A1:AM56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7415,6 +7415,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1755</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1178</v>
+      </c>
+      <c r="E56" t="n">
+        <v>576</v>
+      </c>
+      <c r="F56" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="G56" t="n">
+        <v>291</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>16.58%</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>10</v>
+      </c>
+      <c r="J56" t="n">
+        <v>300</v>
+      </c>
+      <c r="K56" t="n">
+        <v>204</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M56" t="n">
+        <v>5.25125</v>
+      </c>
+      <c r="N56" t="n">
+        <v>32.46625</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.001818181818181719</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>-0.3799999999999955</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-0.01143889223359407</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.4299999999999997</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.08464566929133843</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.3600000000000065</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.01108374384236477</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
